--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T13:41:42+00:00</t>
+    <t>2025-02-27T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T09:48:09+00:00</t>
+    <t>2025-03-04T08:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:17:54+00:00</t>
+    <t>2025-03-06T14:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:47:34+00:00</t>
+    <t>2025-03-07T13:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:06:03+00:00</t>
+    <t>2025-04-23T14:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2735,17 +2735,17 @@
   <dimension ref="A1:AP176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="67.33984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2754,28 +2754,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="83.1953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="26.1796875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.4453125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T14:15:06+00:00</t>
+    <t>2025-05-21T14:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:16+00:00</t>
+    <t>2025-07-21T12:31:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:31:31+00:00</t>
+    <t>2025-10-13T07:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5782,7 +5782,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>270</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>276</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>289</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>307</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>343</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>380</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>407</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>447</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>449</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>497</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>514</v>
       </c>
@@ -14096,7 +14096,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>601</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>607</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>616</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>626</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>631</v>
       </c>
@@ -17116,7 +17116,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>665</v>
       </c>
@@ -17360,7 +17360,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>686</v>
       </c>
@@ -17480,7 +17480,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>694</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>703</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>711</v>
       </c>
@@ -18088,7 +18088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>714</v>
       </c>
@@ -18572,7 +18572,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>720</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>740</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>742</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>743</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>744</v>
       </c>
@@ -21104,7 +21104,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>745</v>
       </c>
@@ -21470,7 +21470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>748</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>754</v>
       </c>
@@ -23522,7 +23522,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>769</v>
       </c>
@@ -23644,7 +23644,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>770</v>
       </c>
@@ -24012,12 +24012,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP176">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
